--- a/data/trans_dic/P1423-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,74</t>
+          <t>1,38; 3,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,26</t>
+          <t>2,49; 5,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,13</t>
+          <t>1,7; 4,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,95</t>
+          <t>5,96; 10,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,47</t>
+          <t>4,65; 8,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 15,83</t>
+          <t>10,56; 15,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 14,38</t>
+          <t>9,61; 14,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,03; 12,34</t>
+          <t>8,36; 12,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,48</t>
+          <t>3,47; 5,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 9,83</t>
+          <t>7,08; 10,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,83</t>
+          <t>5,88; 8,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,62; 10,53</t>
+          <t>7,76; 10,61</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,28</t>
+          <t>1,96; 4,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,3</t>
+          <t>3,44; 6,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,24</t>
+          <t>1,4; 3,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,44</t>
+          <t>1,75; 5,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,61</t>
+          <t>6,17; 9,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 13,55</t>
+          <t>9,35; 13,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,95</t>
+          <t>7,21; 10,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,04</t>
+          <t>9,8; 13,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,54</t>
+          <t>4,35; 6,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 9,3</t>
+          <t>6,78; 9,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,82</t>
+          <t>4,74; 6,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,46</t>
+          <t>4,84; 8,53</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,98</t>
+          <t>2,35; 5,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,98</t>
+          <t>1,96; 5,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,23</t>
+          <t>2,39; 5,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,1</t>
+          <t>4,19; 8,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,05</t>
+          <t>6,19; 10,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,49</t>
+          <t>7,94; 12,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 11,47</t>
+          <t>7,3; 11,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 14,15</t>
+          <t>4,68; 14,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,01</t>
+          <t>4,6; 7,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,15</t>
+          <t>5,47; 8,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 7,9</t>
+          <t>5,22; 7,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,33</t>
+          <t>5,73; 10,27</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,84</t>
+          <t>2,48; 4,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,3</t>
+          <t>3,42; 6,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,15</t>
+          <t>3,24; 6,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,39</t>
+          <t>5,22; 8,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 9,79</t>
+          <t>6,38; 9,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,59; 13,5</t>
+          <t>9,57; 13,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 13,38</t>
+          <t>8,93; 13,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 13,78</t>
+          <t>9,65; 14,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,04</t>
+          <t>4,91; 7,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,59</t>
+          <t>7,01; 9,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 9,28</t>
+          <t>6,73; 9,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,79</t>
+          <t>8,18; 10,76</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,7</t>
+          <t>2,52; 3,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,95</t>
+          <t>3,47; 4,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,93</t>
+          <t>2,69; 3,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,7</t>
+          <t>4,5; 6,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,54</t>
+          <t>6,72; 8,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,24; 12,41</t>
+          <t>10,32; 12,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 11,27</t>
+          <t>9,13; 11,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,34</t>
+          <t>9,01; 12,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,99</t>
+          <t>4,91; 5,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,59</t>
+          <t>7,26; 8,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 7,43</t>
+          <t>6,26; 7,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 9,39</t>
+          <t>7,33; 9,33</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10183; 25982</t>
+          <t>9611; 25747</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17171; 36974</t>
+          <t>17505; 37484</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11291; 27898</t>
+          <t>11475; 28385</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36824; 63249</t>
+          <t>37901; 63922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32802; 58311</t>
+          <t>32028; 57916</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74184; 110344</t>
+          <t>73577; 109406</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63621; 96758</t>
+          <t>64681; 99072</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58242; 89487</t>
+          <t>60644; 91040</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47337; 75745</t>
+          <t>47975; 77500</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96792; 137688</t>
+          <t>99110; 140561</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80440; 118931</t>
+          <t>79231; 117615</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>103660; 143308</t>
+          <t>105552; 144428</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18577; 41205</t>
+          <t>18837; 40848</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34347; 64146</t>
+          <t>35067; 65306</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14265; 33134</t>
+          <t>14317; 32569</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23273; 64943</t>
+          <t>20891; 63437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59859; 93077</t>
+          <t>59779; 93128</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>97997; 139379</t>
+          <t>96209; 138678</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76382; 114221</t>
+          <t>75149; 114505</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>93820; 124986</t>
+          <t>93972; 125334</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>84484; 126189</t>
+          <t>84004; 126739</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>142097; 190438</t>
+          <t>138755; 192234</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94348; 140896</t>
+          <t>97874; 138339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>100792; 182052</t>
+          <t>104092; 183517</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15029; 33795</t>
+          <t>15932; 34727</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15068; 37760</t>
+          <t>14867; 38639</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18835; 39695</t>
+          <t>18170; 39998</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30403; 57044</t>
+          <t>29496; 57975</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40158; 68752</t>
+          <t>42317; 68800</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61386; 97061</t>
+          <t>61732; 97077</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55512; 90068</t>
+          <t>57321; 90610</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54487; 132071</t>
+          <t>43683; 134457</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62982; 95515</t>
+          <t>62732; 96632</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84374; 125041</t>
+          <t>83979; 125970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82298; 122024</t>
+          <t>80626; 120942</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92606; 169143</t>
+          <t>93780; 168237</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23497; 45593</t>
+          <t>23374; 46095</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32450; 59683</t>
+          <t>32387; 60460</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30260; 57629</t>
+          <t>30343; 56666</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47771; 77740</t>
+          <t>48342; 78826</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68098; 101658</t>
+          <t>66299; 103419</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>100902; 141956</t>
+          <t>100681; 144632</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>95950; 139619</t>
+          <t>93179; 138725</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>103706; 150869</t>
+          <t>105641; 154053</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96693; 139394</t>
+          <t>97327; 138798</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>141598; 191710</t>
+          <t>140167; 191641</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>132434; 183885</t>
+          <t>133302; 181908</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>164760; 218213</t>
+          <t>165414; 217529</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82495; 121211</t>
+          <t>82672; 122507</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>119409; 169596</t>
+          <t>118968; 168850</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92138; 133487</t>
+          <t>91379; 132771</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156248; 231927</t>
+          <t>155788; 229127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>226831; 288464</t>
+          <t>226997; 288276</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>364180; 441185</t>
+          <t>366728; 444837</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>327383; 399455</t>
+          <t>323651; 398752</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>333079; 458157</t>
+          <t>334413; 455450</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>324573; 398476</t>
+          <t>326547; 396959</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>504880; 599533</t>
+          <t>506773; 597587</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>425952; 515234</t>
+          <t>434571; 519549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>533889; 673135</t>
+          <t>525435; 669137</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1423-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,71</t>
+          <t>1,38; 3,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,33</t>
+          <t>2,47; 5,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,21</t>
+          <t>1,66; 4,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,06</t>
+          <t>5,81; 9,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,41</t>
+          <t>4,86; 8,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,56; 15,7</t>
+          <t>10,47; 15,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 14,72</t>
+          <t>9,31; 14,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 12,55</t>
+          <t>9,54; 13,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,61</t>
+          <t>3,3; 5,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 10,04</t>
+          <t>6,91; 9,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 8,73</t>
+          <t>5,89; 8,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 10,61</t>
+          <t>8,29; 11,05</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,25</t>
+          <t>1,95; 4,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,42</t>
+          <t>3,4; 6,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,19</t>
+          <t>1,4; 3,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,32</t>
+          <t>3,37; 5,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,62</t>
+          <t>6,17; 9,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,48</t>
+          <t>9,43; 13,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,98</t>
+          <t>7,25; 11,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,07</t>
+          <t>9,7; 12,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,57</t>
+          <t>4,35; 6,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 9,39</t>
+          <t>6,85; 9,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,7</t>
+          <t>4,57; 6,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,53</t>
+          <t>6,93; 8,99</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,12</t>
+          <t>2,33; 5,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,1</t>
+          <t>2,06; 5,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,27</t>
+          <t>2,46; 5,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,23</t>
+          <t>4,0; 7,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,06</t>
+          <t>5,98; 9,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 12,49</t>
+          <t>7,88; 12,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 11,54</t>
+          <t>7,17; 11,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 14,41</t>
+          <t>11,39; 15,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,09</t>
+          <t>4,6; 7,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,21</t>
+          <t>5,5; 8,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,83</t>
+          <t>5,27; 7,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,27</t>
+          <t>8,31; 11,33</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,89</t>
+          <t>2,49; 5,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,38</t>
+          <t>3,32; 6,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,04</t>
+          <t>3,26; 5,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,5</t>
+          <t>5,6; 8,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,96</t>
+          <t>6,37; 9,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 13,75</t>
+          <t>9,52; 13,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 13,29</t>
+          <t>9,12; 13,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 14,07</t>
+          <t>11,01; 14,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,01</t>
+          <t>4,93; 7,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 9,58</t>
+          <t>7,0; 9,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 9,18</t>
+          <t>6,79; 9,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 10,76</t>
+          <t>8,8; 11,23</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,74</t>
+          <t>2,54; 3,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,93</t>
+          <t>3,43; 4,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,91</t>
+          <t>2,71; 3,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,62</t>
+          <t>5,29; 7,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,53</t>
+          <t>6,57; 8,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,32; 12,51</t>
+          <t>10,44; 12,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 11,25</t>
+          <t>9,12; 11,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 12,27</t>
+          <t>11,32; 13,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,96</t>
+          <t>4,78; 5,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 8,56</t>
+          <t>7,23; 8,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,49</t>
+          <t>6,26; 7,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 9,33</t>
+          <t>8,54; 9,81</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>52421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>76039</t>
+          <t>82123</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>124739</t>
+          <t>134544</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9611; 25747</t>
+          <t>9559; 24682</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17505; 37484</t>
+          <t>17361; 37399</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11475; 28385</t>
+          <t>11195; 28157</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37901; 63922</t>
+          <t>40147; 68680</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32028; 57916</t>
+          <t>33446; 58374</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73577; 109406</t>
+          <t>72989; 107902</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64681; 99072</t>
+          <t>62667; 95418</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60644; 91040</t>
+          <t>70017; 97067</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47975; 77500</t>
+          <t>45683; 77306</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>99110; 140561</t>
+          <t>96720; 137813</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79231; 117615</t>
+          <t>79310; 117886</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>105552; 144428</t>
+          <t>118133; 157468</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>48939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>108805</t>
+          <t>120663</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>153461</t>
+          <t>169601</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18837; 40848</t>
+          <t>18770; 39578</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35067; 65306</t>
+          <t>34661; 63427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14317; 32569</t>
+          <t>14355; 32701</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20891; 63437</t>
+          <t>35373; 62288</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59779; 93128</t>
+          <t>59734; 95324</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96209; 138678</t>
+          <t>97008; 137266</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75149; 114505</t>
+          <t>75608; 115318</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>93972; 125334</t>
+          <t>103932; 139105</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>84004; 126739</t>
+          <t>83908; 122849</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138755; 192234</t>
+          <t>140220; 192284</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97874; 138339</t>
+          <t>94458; 139629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>104092; 183517</t>
+          <t>146992; 190729</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40951</t>
+          <t>44872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>97737</t>
+          <t>111673</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>138688</t>
+          <t>156545</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15932; 34727</t>
+          <t>15786; 35598</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14867; 38639</t>
+          <t>15610; 39246</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18170; 39998</t>
+          <t>18702; 41267</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29496; 57975</t>
+          <t>32147; 61240</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42317; 68800</t>
+          <t>40910; 67661</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61732; 97077</t>
+          <t>61277; 96946</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57321; 90610</t>
+          <t>56279; 90163</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43683; 134457</t>
+          <t>92520; 128057</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62732; 96632</t>
+          <t>62642; 97159</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83979; 125970</t>
+          <t>84349; 124989</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80626; 120942</t>
+          <t>81377; 120102</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93780; 168237</t>
+          <t>134195; 182964</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63059</t>
+          <t>68815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>130546</t>
+          <t>142172</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>193605</t>
+          <t>210987</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23374; 46095</t>
+          <t>23483; 47148</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32387; 60460</t>
+          <t>31483; 60288</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30343; 56666</t>
+          <t>30587; 55709</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48342; 78826</t>
+          <t>55483; 88049</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66299; 103419</t>
+          <t>66161; 102143</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>100681; 144632</t>
+          <t>100171; 140709</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93179; 138725</t>
+          <t>95180; 137734</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>105641; 154053</t>
+          <t>123247; 163226</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97327; 138798</t>
+          <t>97695; 139595</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>140167; 191641</t>
+          <t>140035; 190926</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>133302; 181908</t>
+          <t>134522; 184094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>165414; 217529</t>
+          <t>185644; 236948</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>197367</t>
+          <t>215047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>413127</t>
+          <t>456631</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>610494</t>
+          <t>671678</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82672; 122507</t>
+          <t>83266; 121468</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>118968; 168850</t>
+          <t>117403; 170544</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91379; 132771</t>
+          <t>91904; 132452</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>155788; 229127</t>
+          <t>186900; 247797</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>226997; 288276</t>
+          <t>222029; 284522</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>366728; 444837</t>
+          <t>371315; 444017</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>323651; 398752</t>
+          <t>323335; 399186</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>334413; 455450</t>
+          <t>422986; 493459</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>326547; 396959</t>
+          <t>318267; 393864</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>506773; 597587</t>
+          <t>504603; 594476</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>434571; 519549</t>
+          <t>434479; 521099</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>525435; 669137</t>
+          <t>620917; 712908</t>
         </is>
       </c>
     </row>
